--- a/docs-数据采集与埋点/一方平台开发基线/Looply-v1.4-详细埋点需求定稿-v1.1.xlsx
+++ b/docs-数据采集与埋点/一方平台开发基线/Looply-v1.4-详细埋点需求定稿-v1.1.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求总览" sheetId="1" r:id="R8a036085fd7b4cb5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="事件处理矩阵" sheetId="2" r:id="R3117d6218f78436b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详细点位" sheetId="3" r:id="Re315ee9e25e8440c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="停止项" sheetId="4" r:id="R01acc10b04934c85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求总览" sheetId="1" r:id="R5ce57cc57b474a50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="事件处理矩阵" sheetId="2" r:id="Rd006400a9ac94e7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详细点位" sheetId="3" r:id="Re32ff5f5b1874c1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="停止项" sheetId="4" r:id="Rf12d9ed25eb94913"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -699,7 +699,7 @@
         <x:v>详细点位</x:v>
       </x:c>
       <x:c r="B2" s="24" t="str">
-        <x:v>客户端事件和权威业务表事实分开</x:v>
+        <x:v>客户端事件与权威业务表事实分开；交易事实完整定义见《Looply 订单与交易数据接入需求 v1.0》</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
         <x:v>250 个点位（客户端 245，权威业务表事实 5）</x:v>
@@ -1284,19 +1284,19 @@
         <x:v>order_created</x:v>
       </x:c>
       <x:c r="B20" s="24" t="str">
-        <x:v>当前尚未从订单权威业务表接入一方分析</x:v>
+        <x:v>权威业务表事实；本工作簿不维护字段定义</x:v>
       </x:c>
       <x:c r="C20" s="24" t="str">
-        <x:v>新增数据平台权威事实接入；不属于Web／SDK埋点范围</x:v>
+        <x:v>完整来源、唯一键、字段与接入要求见《Looply 订单与交易数据接入需求 v1.0》</x:v>
       </x:c>
       <x:c r="D20" s="24" t="str">
-        <x:v>订单表原始权威数据</x:v>
+        <x:v>不属于Web／SDK事件</x:v>
       </x:c>
       <x:c r="E20" s="24" t="str">
-        <x:v>数据平台按order_id同步并去重</x:v>
+        <x:v>不在本工作簿重复定义</x:v>
       </x:c>
       <x:c r="F20" s="24" t="str">
-        <x:v>数据平台／订单表同步</x:v>
+        <x:v>报表数据接入／数仓任务</x:v>
       </x:c>
       <x:c r="G20" s="24"/>
       <x:c r="H20" s="25"/>
@@ -1306,19 +1306,19 @@
         <x:v>payment_started</x:v>
       </x:c>
       <x:c r="B21" s="24" t="str">
-        <x:v>当前尚未从支付尝试权威表接入一方分析</x:v>
+        <x:v>权威业务表事实；本工作簿不维护字段定义</x:v>
       </x:c>
       <x:c r="C21" s="24" t="str">
-        <x:v>新增数据平台权威事实接入；不属于Web／SDK埋点范围</x:v>
+        <x:v>完整来源、唯一键、字段与接入要求见《Looply 订单与交易数据接入需求 v1.0》</x:v>
       </x:c>
       <x:c r="D21" s="24" t="str">
-        <x:v>支付尝试表原始权威数据</x:v>
+        <x:v>不属于Web／SDK事件</x:v>
       </x:c>
       <x:c r="E21" s="24" t="str">
-        <x:v>数据平台按payment_attempt_id同步并去重</x:v>
+        <x:v>不在本工作簿重复定义</x:v>
       </x:c>
       <x:c r="F21" s="24" t="str">
-        <x:v>数据平台／支付尝试表同步</x:v>
+        <x:v>报表数据接入／数仓任务</x:v>
       </x:c>
       <x:c r="G21" s="24"/>
       <x:c r="H21" s="25"/>
@@ -1328,19 +1328,19 @@
         <x:v>payment_failed</x:v>
       </x:c>
       <x:c r="B22" s="24" t="str">
-        <x:v>当前尚未从支付结果权威表接入一方分析；Web／SDK不生成支付失败事实</x:v>
+        <x:v>权威业务表事实；本工作簿不维护字段定义</x:v>
       </x:c>
       <x:c r="C22" s="24" t="str">
-        <x:v>新增数据平台权威事实接入；不属于Web／SDK埋点范围</x:v>
+        <x:v>完整来源、唯一键、字段与接入要求见《Looply 订单与交易数据接入需求 v1.0》</x:v>
       </x:c>
       <x:c r="D22" s="24" t="str">
-        <x:v>支付失败权威业务表数据；客户端公共failure_type不适用</x:v>
+        <x:v>不属于Web／SDK事件</x:v>
       </x:c>
       <x:c r="E22" s="24" t="str">
-        <x:v>数据平台只同步明确失败终态；失败原因来源字段、分类映射和值域在独立数据平台接入任务中定义，不阻塞Web／SDK</x:v>
+        <x:v>不在本工作簿重复定义</x:v>
       </x:c>
       <x:c r="F22" s="24" t="str">
-        <x:v>数据平台／支付结果表同步</x:v>
+        <x:v>报表数据接入／数仓任务</x:v>
       </x:c>
       <x:c r="G22" s="24"/>
       <x:c r="H22" s="25"/>
@@ -1350,19 +1350,19 @@
         <x:v>purchase</x:v>
       </x:c>
       <x:c r="B23" s="24" t="str">
-        <x:v>当前无真实成交一方事实；Flink的purchase仅是checkout_start历史代理，不代表成交</x:v>
+        <x:v>权威业务表事实；本工作簿不维护字段定义</x:v>
       </x:c>
       <x:c r="C23" s="24" t="str">
-        <x:v>新增数据平台权威成交事实；与Flink历史代理严格隔离；不属于Web／SDK埋点范围</x:v>
+        <x:v>完整来源、唯一键、字段与接入要求见《Looply 订单与交易数据接入需求 v1.0》</x:v>
       </x:c>
       <x:c r="D23" s="24" t="str">
-        <x:v>订单／支付权威成交数据；不得使用Flink历史代理替代</x:v>
+        <x:v>不属于Web／SDK事件</x:v>
       </x:c>
       <x:c r="E23" s="24" t="str">
-        <x:v>数据平台按order_id同步并去重；仅真实支付成功且订单成交事实成立时计入一方purchase</x:v>
+        <x:v>不在本工作簿重复定义</x:v>
       </x:c>
       <x:c r="F23" s="24" t="str">
-        <x:v>数据平台／订单及支付表同步</x:v>
+        <x:v>报表数据接入／数仓任务</x:v>
       </x:c>
       <x:c r="G23" s="24"/>
       <x:c r="H23" s="25"/>
@@ -1372,19 +1372,19 @@
         <x:v>refund</x:v>
       </x:c>
       <x:c r="B24" s="27" t="str">
-        <x:v>当前尚未从退款／售后权威表接入一方分析</x:v>
+        <x:v>权威业务表事实；本工作簿不维护字段定义</x:v>
       </x:c>
       <x:c r="C24" s="27" t="str">
-        <x:v>新增数据平台权威事实接入；不属于Web／SDK埋点范围</x:v>
+        <x:v>完整来源、唯一键、字段与接入要求见《Looply 订单与交易数据接入需求 v1.0》</x:v>
       </x:c>
       <x:c r="D24" s="27" t="str">
-        <x:v>退款／售后权威数据</x:v>
+        <x:v>不属于Web／SDK事件</x:v>
       </x:c>
       <x:c r="E24" s="27" t="str">
-        <x:v>数据平台按refund_id同步并去重</x:v>
+        <x:v>不在本工作簿重复定义</x:v>
       </x:c>
       <x:c r="F24" s="27" t="str">
-        <x:v>数据平台／退款及售后表同步</x:v>
+        <x:v>报表数据接入／数仓任务</x:v>
       </x:c>
       <x:c r="G24" s="27"/>
       <x:c r="H24" s="28"/>
@@ -8411,26 +8411,26 @@
         <x:v>refund</x:v>
       </x:c>
       <x:c r="E191" s="70" t="str">
-        <x:v>数据平台读取退款／售后权威表中已成立的退款事实；按 refund_id 去重。</x:v>
+        <x:v>完整来源、唯一键、字段、存储与接入要求见《Looply 订单与交易数据接入需求 v1.0》；不属于Web／SDK事件。</x:v>
       </x:c>
       <x:c r="F191" s="70" t="str">
-        <x:v>refund_id；order_id；退款时间；amount；currency；items[]（order_item_id、listing_public_code、行退款金额）</x:v>
+        <x:v>见《Looply 订单与交易数据接入需求 v1.0》</x:v>
       </x:c>
       <x:c r="G191" s="70" t="str">
-        <x:v>当前尚未从退款／售后权威表接入一方分析</x:v>
+        <x:v>权威业务表事实；本工作簿不维护字段定义</x:v>
       </x:c>
       <x:c r="H191" s="70" t="str">
-        <x:v>新增数据平台权威事实接入；不属于Web／SDK埋点范围</x:v>
+        <x:v>按《Looply 订单与交易数据接入需求 v1.0》实施</x:v>
       </x:c>
       <x:c r="I191" s="70" t="str">
-        <x:v>退款／售后权威数据</x:v>
+        <x:v>权威业务表原始事实</x:v>
       </x:c>
       <x:c r="J191" s="70" t="str">
-        <x:v>数据平台按 refund_id 同步并去重</x:v>
+        <x:v>见《Looply 订单与交易数据接入需求 v1.0》</x:v>
       </x:c>
       <x:c r="K191" s="70"/>
       <x:c r="L191" s="70" t="str">
-        <x:v>与退款表核对退款单数、退款金额和退款商品行。</x:v>
+        <x:v>本行仅作为报表逻辑事实名索引；不在本表重复维护交易事实定义。</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="78" customHeight="1">
@@ -10529,26 +10529,26 @@
         <x:v>order_created</x:v>
       </x:c>
       <x:c r="E247" s="70" t="str">
-        <x:v>订单事务成功持久化后，数据平台读取订单权威表形成分析事实；按 order_id 去重。</x:v>
+        <x:v>完整来源、唯一键、字段、存储与接入要求见《Looply 订单与交易数据接入需求 v1.0》；不属于Web／SDK事件。</x:v>
       </x:c>
       <x:c r="F247" s="70" t="str">
-        <x:v>order_id；创建时间；amount；currency；items[]（order_item_id、listing_public_code）；origin_session_id（可确定时）</x:v>
+        <x:v>见《Looply 订单与交易数据接入需求 v1.0》</x:v>
       </x:c>
       <x:c r="G247" s="70" t="str">
-        <x:v>当前尚未从订单权威业务表接入一方分析</x:v>
+        <x:v>权威业务表事实；本工作簿不维护字段定义</x:v>
       </x:c>
       <x:c r="H247" s="70" t="str">
-        <x:v>新增数据平台权威事实接入；不属于Web／SDK埋点范围</x:v>
+        <x:v>按《Looply 订单与交易数据接入需求 v1.0》实施</x:v>
       </x:c>
       <x:c r="I247" s="70" t="str">
-        <x:v>订单表原始权威数据</x:v>
+        <x:v>权威业务表原始事实</x:v>
       </x:c>
       <x:c r="J247" s="70" t="str">
-        <x:v>数据平台按 order_id 同步并去重</x:v>
+        <x:v>见《Looply 订单与交易数据接入需求 v1.0》</x:v>
       </x:c>
       <x:c r="K247" s="70"/>
       <x:c r="L247" s="70" t="str">
-        <x:v>与订单表核对真实创建订单数、金额和订单商品行。</x:v>
+        <x:v>本行仅作为报表逻辑事实名索引；不在本表重复维护交易事实定义。</x:v>
       </x:c>
     </x:row>
     <x:row r="248" ht="78" customHeight="1">
@@ -10565,26 +10565,26 @@
         <x:v>payment_started</x:v>
       </x:c>
       <x:c r="E248" s="70" t="str">
-        <x:v>支付尝试记录真实建立后，数据平台读取支付尝试权威表形成分析事实；按 payment_attempt_id 去重。</x:v>
+        <x:v>完整来源、唯一键、字段、存储与接入要求见《Looply 订单与交易数据接入需求 v1.0》；不属于Web／SDK事件。</x:v>
       </x:c>
       <x:c r="F248" s="70" t="str">
-        <x:v>payment_attempt_id；order_id；payment_type；开始时间</x:v>
+        <x:v>见《Looply 订单与交易数据接入需求 v1.0》</x:v>
       </x:c>
       <x:c r="G248" s="70" t="str">
-        <x:v>当前尚未从支付尝试权威表接入一方分析</x:v>
+        <x:v>权威业务表事实；本工作簿不维护字段定义</x:v>
       </x:c>
       <x:c r="H248" s="70" t="str">
-        <x:v>新增数据平台权威事实接入；不属于Web／SDK埋点范围</x:v>
+        <x:v>按《Looply 订单与交易数据接入需求 v1.0》实施</x:v>
       </x:c>
       <x:c r="I248" s="70" t="str">
-        <x:v>支付尝试表原始权威数据</x:v>
+        <x:v>权威业务表原始事实</x:v>
       </x:c>
       <x:c r="J248" s="70" t="str">
-        <x:v>数据平台按 payment_attempt_id 同步并去重</x:v>
+        <x:v>见《Looply 订单与交易数据接入需求 v1.0》</x:v>
       </x:c>
       <x:c r="K248" s="70"/>
       <x:c r="L248" s="70" t="str">
-        <x:v>统计真实支付尝试次数和支付方式分布，不以 Pay Now 点击代替。</x:v>
+        <x:v>本行仅作为报表逻辑事实名索引；不在本表重复维护交易事实定义。</x:v>
       </x:c>
     </x:row>
     <x:row r="249" ht="78" customHeight="1">
@@ -10601,26 +10601,26 @@
         <x:v>payment_failed</x:v>
       </x:c>
       <x:c r="E249" s="24" t="str">
-        <x:v>支付尝试进入明确失败终态后，数据平台读取支付结果权威表形成分析事实；按 payment_attempt_id 去重。</x:v>
+        <x:v>完整来源、唯一键、字段、存储与接入要求见《Looply 订单与交易数据接入需求 v1.0》；不属于Web／SDK事件。</x:v>
       </x:c>
       <x:c r="F249" s="24" t="str">
-        <x:v>payment_attempt_id；order_id；失败时间；支付失败原因分类属于独立数据平台接入规则，由该任务定义业务表来源字段、封闭枚举、映射与质量校验；本期Web／SDK不传；不使用客户端公共failure_type；不读取或落地支付网关原始错误文本</x:v>
+        <x:v>见《Looply 订单与交易数据接入需求 v1.0》</x:v>
       </x:c>
       <x:c r="G249" s="24" t="str">
-        <x:v>当前尚未从支付结果权威表接入一方分析；Web／SDK不生成支付失败事实</x:v>
+        <x:v>权威业务表事实；本工作簿不维护字段定义</x:v>
       </x:c>
       <x:c r="H249" s="24" t="str">
-        <x:v>新增数据平台权威事实接入；不属于Web／SDK埋点范围</x:v>
+        <x:v>按《Looply 订单与交易数据接入需求 v1.0》实施</x:v>
       </x:c>
       <x:c r="I249" s="24" t="str">
-        <x:v>支付失败权威业务表数据；客户端公共failure_type不适用</x:v>
+        <x:v>权威业务表原始事实</x:v>
       </x:c>
       <x:c r="J249" s="24" t="str">
-        <x:v>数据平台只同步明确失败终态；失败原因映射和DataWorks质量规则另行定义</x:v>
+        <x:v>见《Looply 订单与交易数据接入需求 v1.0》</x:v>
       </x:c>
       <x:c r="K249" s="24"/>
       <x:c r="L249" s="25" t="str">
-        <x:v>统计真实支付失败量；失败原因分类在独立数据平台接入任务中定义，不属于Web／SDK埋点实施或验收范围。</x:v>
+        <x:v>本行仅作为报表逻辑事实名索引；不在本表重复维护交易事实定义。</x:v>
       </x:c>
     </x:row>
     <x:row r="250" ht="78" customHeight="1">
@@ -10637,26 +10637,26 @@
         <x:v>purchase</x:v>
       </x:c>
       <x:c r="E250" s="70" t="str">
-        <x:v>支付成功且订单成交事实成立后，数据平台读取订单／支付权威表形成成交事实；同一 order_id 只形成一次。</x:v>
+        <x:v>完整来源、唯一键、字段、存储与接入要求见《Looply 订单与交易数据接入需求 v1.0》；不属于Web／SDK事件。</x:v>
       </x:c>
       <x:c r="F250" s="70" t="str">
-        <x:v>order_id；支付成功时间；amount；currency；items[]（order_item_id、listing_public_code、行成交金额）；origin_session_id（可确定时）</x:v>
+        <x:v>见《Looply 订单与交易数据接入需求 v1.0》</x:v>
       </x:c>
       <x:c r="G250" s="70" t="str">
-        <x:v>当前无真实成交一方事实；Flink的purchase仅是checkout_start历史代理，不代表成交</x:v>
+        <x:v>权威业务表事实；本工作簿不维护字段定义</x:v>
       </x:c>
       <x:c r="H250" s="70" t="str">
-        <x:v>新增数据平台权威成交事实；与Flink历史代理严格隔离；不属于Web／SDK埋点范围</x:v>
+        <x:v>按《Looply 订单与交易数据接入需求 v1.0》实施</x:v>
       </x:c>
       <x:c r="I250" s="70" t="str">
-        <x:v>订单／支付权威成交数据；不得使用Flink历史代理替代</x:v>
+        <x:v>权威业务表原始事实</x:v>
       </x:c>
       <x:c r="J250" s="70" t="str">
-        <x:v>数据平台按order_id同步并去重；仅真实支付成功且订单成交事实成立时计入一方purchase</x:v>
+        <x:v>见《Looply 订单与交易数据接入需求 v1.0》</x:v>
       </x:c>
       <x:c r="K250" s="70"/>
       <x:c r="L250" s="70" t="str">
-        <x:v>与权威业务表核对成交订单数、成交金额和订单商品行。</x:v>
+        <x:v>本行仅作为报表逻辑事实名索引；不在本表重复维护交易事实定义。</x:v>
       </x:c>
     </x:row>
     <x:row r="251" ht="78" customHeight="1">
